--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,642 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128340007</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Näsberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>533075</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6851740</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128340289</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Näsberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>533089</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6851770</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128340290</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92637</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Näsberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>533081</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6851767</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128340009</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79620</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Näsberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>533216</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6851604</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128340010</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Näsberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>533219</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6851605</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128340008</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Näsberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>533166</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6851609</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128340007</v>
       </c>
       <c r="B3" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128340289</v>
       </c>
       <c r="B4" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340290</v>
       </c>
       <c r="B5" t="n">
-        <v>92637</v>
+        <v>92642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340009</v>
+        <v>128340010</v>
       </c>
       <c r="B6" t="n">
-        <v>79620</v>
+        <v>78790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533216</v>
+        <v>533219</v>
       </c>
       <c r="R6" t="n">
-        <v>6851604</v>
+        <v>6851605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340010</v>
+        <v>128340009</v>
       </c>
       <c r="B7" t="n">
-        <v>78789</v>
+        <v>79621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533219</v>
+        <v>533216</v>
       </c>
       <c r="R7" t="n">
-        <v>6851605</v>
+        <v>6851604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
         <v>128340008</v>
       </c>
       <c r="B8" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128340007</v>
       </c>
       <c r="B3" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340289</v>
+        <v>128340290</v>
       </c>
       <c r="B4" t="n">
-        <v>92650</v>
+        <v>92734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533089</v>
+        <v>533081</v>
       </c>
       <c r="R4" t="n">
-        <v>6851770</v>
+        <v>6851767</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340290</v>
+        <v>128340289</v>
       </c>
       <c r="B5" t="n">
-        <v>92642</v>
+        <v>92742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533081</v>
+        <v>533089</v>
       </c>
       <c r="R5" t="n">
-        <v>6851767</v>
+        <v>6851770</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1107,7 @@
         <v>128340010</v>
       </c>
       <c r="B6" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128340009</v>
       </c>
       <c r="B7" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>128340008</v>
       </c>
       <c r="B8" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340290</v>
+        <v>128340289</v>
       </c>
       <c r="B4" t="n">
-        <v>92734</v>
+        <v>92742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533081</v>
+        <v>533089</v>
       </c>
       <c r="R4" t="n">
-        <v>6851767</v>
+        <v>6851770</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340289</v>
+        <v>128340290</v>
       </c>
       <c r="B5" t="n">
-        <v>92742</v>
+        <v>92734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533089</v>
+        <v>533081</v>
       </c>
       <c r="R5" t="n">
-        <v>6851770</v>
+        <v>6851767</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128340007</v>
       </c>
       <c r="B3" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128340289</v>
       </c>
       <c r="B4" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340290</v>
       </c>
       <c r="B5" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128340010</v>
       </c>
       <c r="B6" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128340009</v>
       </c>
       <c r="B7" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>128340008</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340010</v>
+        <v>128340009</v>
       </c>
       <c r="B6" t="n">
-        <v>78844</v>
+        <v>79677</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533219</v>
+        <v>533216</v>
       </c>
       <c r="R6" t="n">
-        <v>6851605</v>
+        <v>6851604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340009</v>
+        <v>128340010</v>
       </c>
       <c r="B7" t="n">
-        <v>79677</v>
+        <v>78844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533216</v>
+        <v>533219</v>
       </c>
       <c r="R7" t="n">
-        <v>6851604</v>
+        <v>6851605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128340007</v>
       </c>
       <c r="B3" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128340289</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340290</v>
       </c>
       <c r="B5" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340009</v>
+        <v>128340010</v>
       </c>
       <c r="B6" t="n">
-        <v>79677</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533216</v>
+        <v>533219</v>
       </c>
       <c r="R6" t="n">
-        <v>6851604</v>
+        <v>6851605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340010</v>
+        <v>128340009</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>79679</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533219</v>
+        <v>533216</v>
       </c>
       <c r="R7" t="n">
-        <v>6851605</v>
+        <v>6851604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
         <v>128340008</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128340007</v>
       </c>
       <c r="B3" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128340289</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340290</v>
       </c>
       <c r="B5" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>128340008</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128340007</v>
       </c>
       <c r="B3" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340289</v>
+        <v>128340290</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>92776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533089</v>
+        <v>533081</v>
       </c>
       <c r="R4" t="n">
-        <v>6851770</v>
+        <v>6851767</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340290</v>
+        <v>128340289</v>
       </c>
       <c r="B5" t="n">
-        <v>92749</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533081</v>
+        <v>533089</v>
       </c>
       <c r="R5" t="n">
-        <v>6851767</v>
+        <v>6851770</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1107,7 @@
         <v>128340010</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128340009</v>
       </c>
       <c r="B7" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>128340008</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340290</v>
+        <v>128340289</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533081</v>
+        <v>533089</v>
       </c>
       <c r="R4" t="n">
-        <v>6851767</v>
+        <v>6851770</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340289</v>
+        <v>128340290</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>92776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533089</v>
+        <v>533081</v>
       </c>
       <c r="R5" t="n">
-        <v>6851770</v>
+        <v>6851767</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340010</v>
+        <v>128340009</v>
       </c>
       <c r="B6" t="n">
-        <v>78873</v>
+        <v>79706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533219</v>
+        <v>533216</v>
       </c>
       <c r="R6" t="n">
-        <v>6851605</v>
+        <v>6851604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340009</v>
+        <v>128340010</v>
       </c>
       <c r="B7" t="n">
-        <v>79706</v>
+        <v>78873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533216</v>
+        <v>533219</v>
       </c>
       <c r="R7" t="n">
-        <v>6851604</v>
+        <v>6851605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128340007</v>
       </c>
       <c r="B3" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128340289</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340290</v>
       </c>
       <c r="B5" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340009</v>
+        <v>128340010</v>
       </c>
       <c r="B6" t="n">
-        <v>79706</v>
+        <v>78877</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533216</v>
+        <v>533219</v>
       </c>
       <c r="R6" t="n">
-        <v>6851604</v>
+        <v>6851605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340010</v>
+        <v>128340009</v>
       </c>
       <c r="B7" t="n">
-        <v>78873</v>
+        <v>79710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533219</v>
+        <v>533216</v>
       </c>
       <c r="R7" t="n">
-        <v>6851605</v>
+        <v>6851604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
         <v>128340008</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128340007</v>
       </c>
       <c r="B3" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128340289</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128340290</v>
       </c>
       <c r="B5" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340010</v>
+        <v>128340009</v>
       </c>
       <c r="B6" t="n">
-        <v>78877</v>
+        <v>79714</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533219</v>
+        <v>533216</v>
       </c>
       <c r="R6" t="n">
-        <v>6851605</v>
+        <v>6851604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340009</v>
+        <v>128340010</v>
       </c>
       <c r="B7" t="n">
-        <v>79710</v>
+        <v>78881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533216</v>
+        <v>533219</v>
       </c>
       <c r="R7" t="n">
-        <v>6851604</v>
+        <v>6851605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
         <v>128340008</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124326765</v>
+        <v>128340290</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533378</v>
+        <v>533081</v>
       </c>
       <c r="R2" t="n">
-        <v>6851764</v>
+        <v>6851767</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,14 +781,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340007</v>
+        <v>124326765</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533075</v>
+        <v>533378</v>
       </c>
       <c r="R3" t="n">
-        <v>6851740</v>
+        <v>6851764</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,17 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,14 +887,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340289</v>
+        <v>128340007</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -931,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533089</v>
+        <v>533075</v>
       </c>
       <c r="R4" t="n">
-        <v>6851770</v>
+        <v>6851740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340290</v>
+        <v>128340008</v>
       </c>
       <c r="B5" t="n">
-        <v>92790</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533081</v>
+        <v>533166</v>
       </c>
       <c r="R5" t="n">
-        <v>6851767</v>
+        <v>6851609</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340009</v>
+        <v>128340289</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533216</v>
+        <v>533089</v>
       </c>
       <c r="R6" t="n">
-        <v>6851604</v>
+        <v>6851770</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
         <v>128340010</v>
       </c>
       <c r="B7" t="n">
-        <v>78881</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340008</v>
+        <v>128340009</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>79917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533166</v>
+        <v>533216</v>
       </c>
       <c r="R8" t="n">
-        <v>6851609</v>
+        <v>6851604</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 42460-2025 artfynd.xlsx
+++ b/artfynd/A 42460-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340290</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326765</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340007</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340008</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340289</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340010</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,8 +1449,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340009</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>